--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/14.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/14.xlsx
@@ -426,13 +426,13 @@
         <v>-9.461658025522951</v>
       </c>
       <c r="E2">
-        <v>-13.03845725873323</v>
+        <v>-14.40769212151402</v>
       </c>
       <c r="F2">
-        <v>1.700837767243952</v>
+        <v>-0.7641823302084965</v>
       </c>
       <c r="G2">
-        <v>-17.54442110528555</v>
+        <v>-17.30603140592641</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.016256137580886</v>
       </c>
       <c r="E3">
-        <v>-13.09132763889829</v>
+        <v>-14.22346397356728</v>
       </c>
       <c r="F3">
-        <v>1.696072997943049</v>
+        <v>-0.6484005899518068</v>
       </c>
       <c r="G3">
-        <v>-16.05578106629424</v>
+        <v>-16.81425458490447</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.455934380171533</v>
       </c>
       <c r="E4">
-        <v>-12.9130801152593</v>
+        <v>-14.93775817647924</v>
       </c>
       <c r="F4">
-        <v>2.048591373143601</v>
+        <v>-0.597712788574505</v>
       </c>
       <c r="G4">
-        <v>-16.91265615928812</v>
+        <v>-16.22039503962541</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.856108637589641</v>
       </c>
       <c r="E5">
-        <v>-12.86825865864175</v>
+        <v>-15.33883794732926</v>
       </c>
       <c r="F5">
-        <v>2.299033346766781</v>
+        <v>-0.5086798601216141</v>
       </c>
       <c r="G5">
-        <v>-15.9774104297859</v>
+        <v>-16.02263505296546</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.235982613709904</v>
       </c>
       <c r="E6">
-        <v>-13.54831794060315</v>
+        <v>-14.74449679390099</v>
       </c>
       <c r="F6">
-        <v>1.662918421013402</v>
+        <v>0.07729233000550571</v>
       </c>
       <c r="G6">
-        <v>-15.21192706194853</v>
+        <v>-15.42321984319651</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.635666924832882</v>
       </c>
       <c r="E7">
-        <v>-14.59837020664823</v>
+        <v>-17.71329531311493</v>
       </c>
       <c r="F7">
-        <v>1.798389626067233</v>
+        <v>-0.4379397690247448</v>
       </c>
       <c r="G7">
-        <v>-15.44680661520493</v>
+        <v>-15.26134715168601</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.076688703671157</v>
       </c>
       <c r="E8">
-        <v>-14.55133093518322</v>
+        <v>-16.8783004826808</v>
       </c>
       <c r="F8">
-        <v>1.860131162067491</v>
+        <v>-0.1471082575758663</v>
       </c>
       <c r="G8">
-        <v>-13.62474838448253</v>
+        <v>-15.06965453545581</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.578208325691229</v>
       </c>
       <c r="E9">
-        <v>-14.99350257888109</v>
+        <v>-18.331824769299</v>
       </c>
       <c r="F9">
-        <v>2.453848587410786</v>
+        <v>-0.02682434048496134</v>
       </c>
       <c r="G9">
-        <v>-13.07287091760087</v>
+        <v>-14.20499550746353</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.148990446425803</v>
       </c>
       <c r="E10">
-        <v>-16.57092961895289</v>
+        <v>-18.31282798069923</v>
       </c>
       <c r="F10">
-        <v>2.646960909821019</v>
+        <v>0.365946891919827</v>
       </c>
       <c r="G10">
-        <v>-13.31483603167754</v>
+        <v>-13.97084696269265</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.788850167293218</v>
       </c>
       <c r="E11">
-        <v>-15.63137769341621</v>
+        <v>-19.32195450234945</v>
       </c>
       <c r="F11">
-        <v>2.372663611732018</v>
+        <v>0.8136264576191806</v>
       </c>
       <c r="G11">
-        <v>-12.87419325421715</v>
+        <v>-13.6008731251968</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.497926983685743</v>
       </c>
       <c r="E12">
-        <v>-17.7584033413139</v>
+        <v>-19.82048937693657</v>
       </c>
       <c r="F12">
-        <v>3.018806753263688</v>
+        <v>0.6620169988240096</v>
       </c>
       <c r="G12">
-        <v>-11.73069626091559</v>
+        <v>-12.95172453633944</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.263622763741567</v>
       </c>
       <c r="E13">
-        <v>-17.39474400450058</v>
+        <v>-19.84214422078422</v>
       </c>
       <c r="F13">
-        <v>2.940214567555683</v>
+        <v>1.23428633537402</v>
       </c>
       <c r="G13">
-        <v>-11.65861751887184</v>
+        <v>-12.67570486981628</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.080472137673823</v>
       </c>
       <c r="E14">
-        <v>-19.2504694290265</v>
+        <v>-20.27141599010718</v>
       </c>
       <c r="F14">
-        <v>3.371646535016527</v>
+        <v>1.611864481244063</v>
       </c>
       <c r="G14">
-        <v>-10.58271270303422</v>
+        <v>-12.70899447409757</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.927691285499677</v>
       </c>
       <c r="E15">
-        <v>-19.6023004199867</v>
+        <v>-21.5177074912504</v>
       </c>
       <c r="F15">
-        <v>3.694883779262922</v>
+        <v>1.561612401120633</v>
       </c>
       <c r="G15">
-        <v>-11.61559505875489</v>
+        <v>-12.64694882351746</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.793711102385962</v>
       </c>
       <c r="E16">
-        <v>-20.55233505090725</v>
+        <v>-21.8513058844946</v>
       </c>
       <c r="F16">
-        <v>4.079377136211535</v>
+        <v>1.809105386789847</v>
       </c>
       <c r="G16">
-        <v>-9.90902572576498</v>
+        <v>-12.35188508057443</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.655939848887602</v>
       </c>
       <c r="E17">
-        <v>-20.3059956275977</v>
+        <v>-22.65596565941218</v>
       </c>
       <c r="F17">
-        <v>3.620047411359209</v>
+        <v>1.947578595311424</v>
       </c>
       <c r="G17">
-        <v>-10.46469529916524</v>
+        <v>-11.86055991836675</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.503005556270717</v>
       </c>
       <c r="E18">
-        <v>-22.23836856712332</v>
+        <v>-23.92501260540414</v>
       </c>
       <c r="F18">
-        <v>4.488284137255455</v>
+        <v>2.29302933983129</v>
       </c>
       <c r="G18">
-        <v>-10.21627250834244</v>
+        <v>-12.35211613147074</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.31960560761707</v>
       </c>
       <c r="E19">
-        <v>-22.60885578335465</v>
+        <v>-24.32218005118617</v>
       </c>
       <c r="F19">
-        <v>4.157435853312138</v>
+        <v>2.697372036485785</v>
       </c>
       <c r="G19">
-        <v>-10.00567549052799</v>
+        <v>-11.76447799055231</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.102080008356236</v>
       </c>
       <c r="E20">
-        <v>-23.24438433349124</v>
+        <v>-24.67006549138778</v>
       </c>
       <c r="F20">
-        <v>4.552908391817455</v>
+        <v>2.35912974510508</v>
       </c>
       <c r="G20">
-        <v>-9.549775521677132</v>
+        <v>-12.20170721945982</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.845817025395255</v>
       </c>
       <c r="E21">
-        <v>-23.38483763407429</v>
+        <v>-26.55202675185264</v>
       </c>
       <c r="F21">
-        <v>5.149533386744577</v>
+        <v>2.856141903110755</v>
       </c>
       <c r="G21">
-        <v>-9.300408946684652</v>
+        <v>-11.4500464388601</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.554505332989679</v>
       </c>
       <c r="E22">
-        <v>-24.90760425990003</v>
+        <v>-26.33248384801088</v>
       </c>
       <c r="F22">
-        <v>5.140336851838697</v>
+        <v>3.033044732183007</v>
       </c>
       <c r="G22">
-        <v>-9.701579876672005</v>
+        <v>-11.20149702692464</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.231768227549462</v>
       </c>
       <c r="E23">
-        <v>-24.72936919589501</v>
+        <v>-27.22363424876801</v>
       </c>
       <c r="F23">
-        <v>4.971114645325202</v>
+        <v>2.571663969641349</v>
       </c>
       <c r="G23">
-        <v>-9.170692796302891</v>
+        <v>-11.05382156450061</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.885609104544355</v>
       </c>
       <c r="E24">
-        <v>-24.18397779114118</v>
+        <v>-27.33996569797646</v>
       </c>
       <c r="F24">
-        <v>5.27548002340102</v>
+        <v>2.917393045608556</v>
       </c>
       <c r="G24">
-        <v>-8.499984678612115</v>
+        <v>-10.85423144588229</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.524737494843669</v>
       </c>
       <c r="E25">
-        <v>-26.54110795927967</v>
+        <v>-28.54373246836477</v>
       </c>
       <c r="F25">
-        <v>5.274312025363072</v>
+        <v>3.090974121395582</v>
       </c>
       <c r="G25">
-        <v>-8.571930272681719</v>
+        <v>-11.2595887048215</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.158688691492065</v>
       </c>
       <c r="E26">
-        <v>-25.25090040158771</v>
+        <v>-28.16042428877369</v>
       </c>
       <c r="F26">
-        <v>5.646623411286115</v>
+        <v>3.093358162780838</v>
       </c>
       <c r="G26">
-        <v>-9.650319211997791</v>
+        <v>-11.0248866821973</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.7985567165179459</v>
       </c>
       <c r="E27">
-        <v>-25.97081389942216</v>
+        <v>-29.09357196244749</v>
       </c>
       <c r="F27">
-        <v>4.957077131317362</v>
+        <v>2.963968831198361</v>
       </c>
       <c r="G27">
-        <v>-8.580497431057458</v>
+        <v>-10.87314367970032</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.452743449551868</v>
       </c>
       <c r="E28">
-        <v>-25.79480080347593</v>
+        <v>-29.83356208382617</v>
       </c>
       <c r="F28">
-        <v>4.764385619547753</v>
+        <v>2.709812458141028</v>
       </c>
       <c r="G28">
-        <v>-7.820229025540836</v>
+        <v>-10.17966073156897</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.1324109525536821</v>
       </c>
       <c r="E29">
-        <v>-24.96900118291497</v>
+        <v>-28.90805424238439</v>
       </c>
       <c r="F29">
-        <v>4.662753222898281</v>
+        <v>3.079811042275455</v>
       </c>
       <c r="G29">
-        <v>-8.246974809542735</v>
+        <v>-9.889626588080713</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.1563028956364597</v>
       </c>
       <c r="E30">
-        <v>-25.82846673447499</v>
+        <v>-29.54515270640176</v>
       </c>
       <c r="F30">
-        <v>4.289040239329701</v>
+        <v>2.709655068334496</v>
       </c>
       <c r="G30">
-        <v>-8.457895559686483</v>
+        <v>-9.653439051784172</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.4046705568588573</v>
       </c>
       <c r="E31">
-        <v>-25.97313554455274</v>
+        <v>-30.08747696459221</v>
       </c>
       <c r="F31">
-        <v>4.521215054986346</v>
+        <v>3.236097463426832</v>
       </c>
       <c r="G31">
-        <v>-8.110526854232791</v>
+        <v>-9.162889280720055</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.6110062361372256</v>
       </c>
       <c r="E32">
-        <v>-25.74116623242709</v>
+        <v>-28.77418170514553</v>
       </c>
       <c r="F32">
-        <v>5.193928909330213</v>
+        <v>2.805823553595102</v>
       </c>
       <c r="G32">
-        <v>-8.315488579847322</v>
+        <v>-9.450862241353622</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.7702127254660343</v>
       </c>
       <c r="E33">
-        <v>-27.04250024325827</v>
+        <v>-29.64064541778788</v>
       </c>
       <c r="F33">
-        <v>5.097288254650012</v>
+        <v>2.737513064090644</v>
       </c>
       <c r="G33">
-        <v>-7.569927803984736</v>
+        <v>-9.031559690180988</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.8839677443105883</v>
       </c>
       <c r="E34">
-        <v>-25.64501108383466</v>
+        <v>-29.68144033602601</v>
       </c>
       <c r="F34">
-        <v>4.761105284632666</v>
+        <v>2.621462104428044</v>
       </c>
       <c r="G34">
-        <v>-8.122529752490435</v>
+        <v>-8.622301978822659</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.9513738891950505</v>
       </c>
       <c r="E35">
-        <v>-25.10587856854734</v>
+        <v>-28.82836865330056</v>
       </c>
       <c r="F35">
-        <v>4.640175240967578</v>
+        <v>2.895322024528366</v>
       </c>
       <c r="G35">
-        <v>-7.65843987785725</v>
+        <v>-8.637241964745305</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.9772014187979641</v>
       </c>
       <c r="E36">
-        <v>-26.72285664006549</v>
+        <v>-28.31515217668018</v>
       </c>
       <c r="F36">
-        <v>4.172710948219761</v>
+        <v>2.88888726654342</v>
       </c>
       <c r="G36">
-        <v>-7.747147757574097</v>
+        <v>-8.147380124880947</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.9653486395637496</v>
       </c>
       <c r="E37">
-        <v>-23.76549606484013</v>
+        <v>-28.51550724420123</v>
       </c>
       <c r="F37">
-        <v>5.262845763773521</v>
+        <v>2.942230813814096</v>
       </c>
       <c r="G37">
-        <v>-8.571444674187772</v>
+        <v>-8.045790831351546</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9215677673277971</v>
       </c>
       <c r="E38">
-        <v>-24.50772061391156</v>
+        <v>-28.45146057236105</v>
       </c>
       <c r="F38">
-        <v>4.949976365940564</v>
+        <v>2.873900443491971</v>
       </c>
       <c r="G38">
-        <v>-8.014747772790914</v>
+        <v>-8.075033781516606</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.8500453581756547</v>
       </c>
       <c r="E39">
-        <v>-23.71457769399773</v>
+        <v>-28.09106981286038</v>
       </c>
       <c r="F39">
-        <v>5.050864888662322</v>
+        <v>3.281245143614211</v>
       </c>
       <c r="G39">
-        <v>-8.38519415505775</v>
+        <v>-7.934943837502058</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.7549268684298016</v>
       </c>
       <c r="E40">
-        <v>-23.31025841831435</v>
+        <v>-27.58015836852527</v>
       </c>
       <c r="F40">
-        <v>4.963684189722091</v>
+        <v>3.108747572390048</v>
       </c>
       <c r="G40">
-        <v>-7.723486579344837</v>
+        <v>-8.144539634765815</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.6404395562332974</v>
       </c>
       <c r="E41">
-        <v>-23.65185589657017</v>
+        <v>-27.58319436600372</v>
       </c>
       <c r="F41">
-        <v>4.953657630678606</v>
+        <v>3.461706639048889</v>
       </c>
       <c r="G41">
-        <v>-8.42117674238477</v>
+        <v>-7.999311745395956</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.51050657383066</v>
       </c>
       <c r="E42">
-        <v>-23.49829090783463</v>
+        <v>-27.78555128138334</v>
       </c>
       <c r="F42">
-        <v>4.99003952700956</v>
+        <v>3.390359354645768</v>
       </c>
       <c r="G42">
-        <v>-7.481533213618823</v>
+        <v>-8.236046232684336</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.3689690737710714</v>
       </c>
       <c r="E43">
-        <v>-23.07805237314318</v>
+        <v>-26.60650027158909</v>
       </c>
       <c r="F43">
-        <v>4.939765909333658</v>
+        <v>3.441414951149912</v>
       </c>
       <c r="G43">
-        <v>-8.087567966298542</v>
+        <v>-8.49312625257126</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.2193547588100789</v>
       </c>
       <c r="E44">
-        <v>-22.41076006279431</v>
+        <v>-27.00338114578971</v>
       </c>
       <c r="F44">
-        <v>5.274479355578437</v>
+        <v>3.519274860073843</v>
       </c>
       <c r="G44">
-        <v>-8.057858998223967</v>
+        <v>-8.47301438161362</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.06454645854988807</v>
       </c>
       <c r="E45">
-        <v>-22.09696833435821</v>
+        <v>-26.80452123434559</v>
       </c>
       <c r="F45">
-        <v>5.093764379718503</v>
+        <v>3.518849079228805</v>
       </c>
       <c r="G45">
-        <v>-7.487381281502916</v>
+        <v>-8.191779752769714</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.09214864955604792</v>
       </c>
       <c r="E46">
-        <v>-22.15898823907187</v>
+        <v>-25.69396498572041</v>
       </c>
       <c r="F46">
-        <v>4.945360702772166</v>
+        <v>3.694789345379003</v>
       </c>
       <c r="G46">
-        <v>-8.110461585618014</v>
+        <v>-9.076839138996961</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.2488873125344211</v>
       </c>
       <c r="E47">
-        <v>-21.10087458984531</v>
+        <v>-24.83994014099592</v>
       </c>
       <c r="F47">
-        <v>5.128630363702334</v>
+        <v>3.635913960592431</v>
       </c>
       <c r="G47">
-        <v>-7.246378226808067</v>
+        <v>-9.158360944226768</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.402434387504526</v>
       </c>
       <c r="E48">
-        <v>-21.58584092303421</v>
+        <v>-25.34483773533268</v>
       </c>
       <c r="F48">
-        <v>4.940688710620377</v>
+        <v>3.331836854372788</v>
       </c>
       <c r="G48">
-        <v>-8.024036802046094</v>
+        <v>-9.526794442413857</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.5527918540860222</v>
       </c>
       <c r="E49">
-        <v>-20.30687195518724</v>
+        <v>-24.95274136057827</v>
       </c>
       <c r="F49">
-        <v>5.005809985624057</v>
+        <v>3.618009627548322</v>
       </c>
       <c r="G49">
-        <v>-8.282517486406151</v>
+        <v>-8.919214128936201</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.6977606181031561</v>
       </c>
       <c r="E50">
-        <v>-20.35158542831034</v>
+        <v>-24.7114356293944</v>
       </c>
       <c r="F50">
-        <v>5.532689758705072</v>
+        <v>3.459080714382015</v>
       </c>
       <c r="G50">
-        <v>-8.652303350291438</v>
+        <v>-9.036668917345796</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8393039968406788</v>
       </c>
       <c r="E51">
-        <v>-19.37243263279141</v>
+        <v>-24.73188188874653</v>
       </c>
       <c r="F51">
-        <v>5.247762850103348</v>
+        <v>3.492049737013435</v>
       </c>
       <c r="G51">
-        <v>-8.747297902983686</v>
+        <v>-9.694396412929557</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.9756350386609021</v>
       </c>
       <c r="E52">
-        <v>-18.74423034743182</v>
+        <v>-23.65269069204646</v>
       </c>
       <c r="F52">
-        <v>5.246883123921575</v>
+        <v>3.514241699734434</v>
       </c>
       <c r="G52">
-        <v>-8.840031550860029</v>
+        <v>-9.502146402729156</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.109628502082791</v>
       </c>
       <c r="E53">
-        <v>-20.53337979442074</v>
+        <v>-23.44121332459752</v>
       </c>
       <c r="F53">
-        <v>4.846322752828263</v>
+        <v>3.364646830462871</v>
       </c>
       <c r="G53">
-        <v>-8.828041706325342</v>
+        <v>-9.633032166687734</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.23927624141771</v>
       </c>
       <c r="E54">
-        <v>-17.49035508240946</v>
+        <v>-23.31351453599301</v>
       </c>
       <c r="F54">
-        <v>4.540279102394374</v>
+        <v>3.745430758181748</v>
       </c>
       <c r="G54">
-        <v>-9.274963324527365</v>
+        <v>-9.569170743244513</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.366415316778161</v>
       </c>
       <c r="E55">
-        <v>-17.53155909196309</v>
+        <v>-22.70084110777696</v>
       </c>
       <c r="F55">
-        <v>4.553549548187222</v>
+        <v>3.521455123078012</v>
       </c>
       <c r="G55">
-        <v>-10.09653201304333</v>
+        <v>-10.05871537764105</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.489153178103562</v>
       </c>
       <c r="E56">
-        <v>-18.57149413522088</v>
+        <v>-21.56045649541686</v>
       </c>
       <c r="F56">
-        <v>4.616136018938336</v>
+        <v>3.608609314261353</v>
       </c>
       <c r="G56">
-        <v>-9.930285018970416</v>
+        <v>-9.999609425470542</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.608788674076514</v>
       </c>
       <c r="E57">
-        <v>-18.48618302139758</v>
+        <v>-22.34671754416545</v>
       </c>
       <c r="F57">
-        <v>4.362637369598826</v>
+        <v>3.714121783825537</v>
       </c>
       <c r="G57">
-        <v>-10.30861193378553</v>
+        <v>-9.945658388495186</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.724046092693283</v>
       </c>
       <c r="E58">
-        <v>-17.85322946228238</v>
+        <v>-21.88525838707508</v>
       </c>
       <c r="F58">
-        <v>4.590892350705424</v>
+        <v>3.899011731395582</v>
       </c>
       <c r="G58">
-        <v>-9.40129072842986</v>
+        <v>-10.09077923733681</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.83563915427169</v>
       </c>
       <c r="E59">
-        <v>-18.38035504362962</v>
+        <v>-21.24193010607046</v>
       </c>
       <c r="F59">
-        <v>4.346586922802183</v>
+        <v>3.833522661265058</v>
       </c>
       <c r="G59">
-        <v>-9.576064414337347</v>
+        <v>-9.866242148778111</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.943667493522111</v>
       </c>
       <c r="E60">
-        <v>-18.28014220757283</v>
+        <v>-21.80250565142787</v>
       </c>
       <c r="F60">
-        <v>5.027385642997373</v>
+        <v>3.929653041625135</v>
       </c>
       <c r="G60">
-        <v>-10.28400436064199</v>
+        <v>-10.51641545488749</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.04860547644078</v>
       </c>
       <c r="E61">
-        <v>-16.64981571485669</v>
+        <v>-21.12383769526028</v>
       </c>
       <c r="F61">
-        <v>4.840530807947888</v>
+        <v>4.177016801979512</v>
       </c>
       <c r="G61">
-        <v>-9.528719866549803</v>
+        <v>-10.37321480869263</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.151777979468902</v>
       </c>
       <c r="E62">
-        <v>-16.32655881781131</v>
+        <v>-21.10009793932756</v>
       </c>
       <c r="F62">
-        <v>4.460906594592931</v>
+        <v>3.974608540575065</v>
       </c>
       <c r="G62">
-        <v>-10.1642273149186</v>
+        <v>-10.76508365570184</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.254770358654242</v>
       </c>
       <c r="E63">
-        <v>-15.74899663813535</v>
+        <v>-20.34632330956178</v>
       </c>
       <c r="F63">
-        <v>5.132826872964917</v>
+        <v>3.964646594188998</v>
       </c>
       <c r="G63">
-        <v>-10.71131928696475</v>
+        <v>-10.67158114354342</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.361927887047112</v>
       </c>
       <c r="E64">
-        <v>-16.36311123068112</v>
+        <v>-20.758209736279</v>
       </c>
       <c r="F64">
-        <v>4.498719909795923</v>
+        <v>3.811020889135412</v>
       </c>
       <c r="G64">
-        <v>-11.10327820466236</v>
+        <v>-11.02781463225623</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.474941198662373</v>
       </c>
       <c r="E65">
-        <v>-15.06252895109974</v>
+        <v>-20.00287349905509</v>
       </c>
       <c r="F65">
-        <v>5.338816995019069</v>
+        <v>3.881655777572127</v>
       </c>
       <c r="G65">
-        <v>-9.813887582120222</v>
+        <v>-10.81736512151118</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.59779089500737</v>
       </c>
       <c r="E66">
-        <v>-16.52801033312211</v>
+        <v>-20.58760827468902</v>
       </c>
       <c r="F66">
-        <v>4.772528471117272</v>
+        <v>4.297304032540029</v>
       </c>
       <c r="G66">
-        <v>-10.30703765479709</v>
+        <v>-11.6442349269194</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.729817369843681</v>
       </c>
       <c r="E67">
-        <v>-16.5647745597695</v>
+        <v>-20.90257536193004</v>
       </c>
       <c r="F67">
-        <v>5.064363963858343</v>
+        <v>3.921733849254372</v>
       </c>
       <c r="G67">
-        <v>-10.6873030474711</v>
+        <v>-11.25788911009268</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.874310052705503</v>
       </c>
       <c r="E68">
-        <v>-15.59984235982678</v>
+        <v>-20.66055943160963</v>
       </c>
       <c r="F68">
-        <v>4.006000351671554</v>
+        <v>4.105916371062426</v>
       </c>
       <c r="G68">
-        <v>-10.75894710054043</v>
+        <v>-11.4709049827708</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.029236638576674</v>
       </c>
       <c r="E69">
-        <v>-14.12657785978168</v>
+        <v>-20.82693707728227</v>
       </c>
       <c r="F69">
-        <v>4.887848810730602</v>
+        <v>4.46888377268189</v>
       </c>
       <c r="G69">
-        <v>-10.92880475438285</v>
+        <v>-11.44465525127945</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.196989355831838</v>
       </c>
       <c r="E70">
-        <v>-16.86491883579221</v>
+        <v>-20.07685049917293</v>
       </c>
       <c r="F70">
-        <v>5.205236124378427</v>
+        <v>4.37907880580959</v>
       </c>
       <c r="G70">
-        <v>-10.31507613739313</v>
+        <v>-11.66436507308918</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.373824399429695</v>
       </c>
       <c r="E71">
-        <v>-16.21477928821487</v>
+        <v>-20.01945727187513</v>
       </c>
       <c r="F71">
-        <v>4.886258345317227</v>
+        <v>4.367609230750428</v>
       </c>
       <c r="G71">
-        <v>-10.39321833374974</v>
+        <v>-12.26221253073117</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.56129729026344</v>
       </c>
       <c r="E72">
-        <v>-17.2841439869204</v>
+        <v>-19.9130312316764</v>
       </c>
       <c r="F72">
-        <v>5.185602160197273</v>
+        <v>3.962000788704456</v>
       </c>
       <c r="G72">
-        <v>-10.35475945517805</v>
+        <v>-12.10077583356738</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.754576688697519</v>
       </c>
       <c r="E73">
-        <v>-17.98789733948995</v>
+        <v>-20.13096684273545</v>
       </c>
       <c r="F73">
-        <v>4.562262316529868</v>
+        <v>4.454016234536445</v>
       </c>
       <c r="G73">
-        <v>-10.11562830435503</v>
+        <v>-12.00278414608453</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.954870338114953</v>
       </c>
       <c r="E74">
-        <v>-16.79982140148685</v>
+        <v>-19.94518124054189</v>
       </c>
       <c r="F74">
-        <v>4.857595176445558</v>
+        <v>4.359130062015373</v>
       </c>
       <c r="G74">
-        <v>-10.92957884015412</v>
+        <v>-12.30475330847106</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.158217072879185</v>
       </c>
       <c r="E75">
-        <v>-17.22795103769547</v>
+        <v>-20.15466091334359</v>
       </c>
       <c r="F75">
-        <v>4.462896333094456</v>
+        <v>4.464741935667893</v>
       </c>
       <c r="G75">
-        <v>-9.63522519214427</v>
+        <v>-12.22808748818072</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.365791056235219</v>
       </c>
       <c r="E76">
-        <v>-18.07854532986565</v>
+        <v>-20.80077599914717</v>
       </c>
       <c r="F76">
-        <v>4.782604732204924</v>
+        <v>4.515741203188647</v>
       </c>
       <c r="G76">
-        <v>-10.58583384819289</v>
+        <v>-12.68722739106916</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.575174768503734</v>
       </c>
       <c r="E77">
-        <v>-17.9665124543784</v>
+        <v>-21.33457163788209</v>
       </c>
       <c r="F77">
-        <v>4.395482137119826</v>
+        <v>4.454523195386958</v>
       </c>
       <c r="G77">
-        <v>-10.36842278699564</v>
+        <v>-12.13234104104624</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.786150848922605</v>
       </c>
       <c r="E78">
-        <v>-17.8963730215247</v>
+        <v>-21.54522251627739</v>
       </c>
       <c r="F78">
-        <v>4.497276893780247</v>
+        <v>4.132526845509957</v>
       </c>
       <c r="G78">
-        <v>-10.04000286578425</v>
+        <v>-12.03212108305488</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.996993375658179</v>
       </c>
       <c r="E79">
-        <v>-17.59637826110968</v>
+        <v>-20.88499481839204</v>
       </c>
       <c r="F79">
-        <v>4.550453110835558</v>
+        <v>4.433956489510252</v>
       </c>
       <c r="G79">
-        <v>-9.125179685846014</v>
+        <v>-12.14564800622714</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.2052441338733</v>
       </c>
       <c r="E80">
-        <v>-18.71110433390499</v>
+        <v>-22.04680584797693</v>
       </c>
       <c r="F80">
-        <v>4.68910856018575</v>
+        <v>4.149437137670706</v>
       </c>
       <c r="G80">
-        <v>-9.990920867471317</v>
+        <v>-11.81875667597385</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.409247605243666</v>
       </c>
       <c r="E81">
-        <v>-19.17261748274259</v>
+        <v>-21.66990192024874</v>
       </c>
       <c r="F81">
-        <v>5.247244292109196</v>
+        <v>4.29130665254376</v>
       </c>
       <c r="G81">
-        <v>-10.48836169888368</v>
+        <v>-12.05118212931459</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.605057897939601</v>
       </c>
       <c r="E82">
-        <v>-20.56330368201613</v>
+        <v>-23.07443907929058</v>
       </c>
       <c r="F82">
-        <v>4.274182641593089</v>
+        <v>4.303216919061212</v>
       </c>
       <c r="G82">
-        <v>-10.13698419511033</v>
+        <v>-11.94836186971048</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.792359991062221</v>
       </c>
       <c r="E83">
-        <v>-19.82444738732913</v>
+        <v>-23.70725142922073</v>
       </c>
       <c r="F83">
-        <v>4.424011110472241</v>
+        <v>4.690848131731629</v>
       </c>
       <c r="G83">
-        <v>-9.499492580852291</v>
+        <v>-11.67495555852303</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.96688157129091</v>
       </c>
       <c r="E84">
-        <v>-22.95330236457931</v>
+        <v>-24.98848389723974</v>
       </c>
       <c r="F84">
-        <v>4.887017129858191</v>
+        <v>3.930554305359381</v>
       </c>
       <c r="G84">
-        <v>-9.56935349536589</v>
+        <v>-11.48758372459113</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.12977841529384</v>
       </c>
       <c r="E85">
-        <v>-22.00177257758181</v>
+        <v>-26.1182404418196</v>
       </c>
       <c r="F85">
-        <v>4.785779036092452</v>
+        <v>4.301803724272036</v>
       </c>
       <c r="G85">
-        <v>-10.13735492084227</v>
+        <v>-11.74918294336527</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.277177835808078</v>
       </c>
       <c r="E86">
-        <v>-24.2445025397779</v>
+        <v>-26.30975332243009</v>
       </c>
       <c r="F86">
-        <v>4.706398244616981</v>
+        <v>4.870845741420739</v>
       </c>
       <c r="G86">
-        <v>-9.636903900916355</v>
+        <v>-11.23502420896371</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.410721574886151</v>
       </c>
       <c r="E87">
-        <v>-25.10002669379066</v>
+        <v>-27.89717714216076</v>
       </c>
       <c r="F87">
-        <v>4.977738271077987</v>
+        <v>4.350215172026444</v>
       </c>
       <c r="G87">
-        <v>-10.06911266797516</v>
+        <v>-11.32423596238664</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.525667966746653</v>
       </c>
       <c r="E88">
-        <v>-27.12270706036336</v>
+        <v>-29.01656311806252</v>
       </c>
       <c r="F88">
-        <v>4.957093698665418</v>
+        <v>5.010899474946857</v>
       </c>
       <c r="G88">
-        <v>-9.447221558021315</v>
+        <v>-11.40584392218796</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.620582719123147</v>
       </c>
       <c r="E89">
-        <v>-26.85342114448412</v>
+        <v>-29.88612927956452</v>
       </c>
       <c r="F89">
-        <v>4.718726008305444</v>
+        <v>4.955822983069524</v>
       </c>
       <c r="G89">
-        <v>-9.060959285021514</v>
+        <v>-11.18619545287612</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.688046730437812</v>
       </c>
       <c r="E90">
-        <v>-30.35210297736499</v>
+        <v>-30.94364278975465</v>
       </c>
       <c r="F90">
-        <v>5.091895582857787</v>
+        <v>5.000543225677058</v>
       </c>
       <c r="G90">
-        <v>-8.455633349498283</v>
+        <v>-10.91320033396177</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.722109029252464</v>
       </c>
       <c r="E91">
-        <v>-30.09585191522873</v>
+        <v>-32.6075500726377</v>
       </c>
       <c r="F91">
-        <v>4.710119270990357</v>
+        <v>4.701167932835705</v>
       </c>
       <c r="G91">
-        <v>-7.916602051377192</v>
+        <v>-10.36551963901032</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.714034083930796</v>
       </c>
       <c r="E92">
-        <v>-32.93736489036498</v>
+        <v>-34.22587586123075</v>
       </c>
       <c r="F92">
-        <v>4.373469101757832</v>
+        <v>4.841213382687795</v>
       </c>
       <c r="G92">
-        <v>-8.956023016926306</v>
+        <v>-10.67081097388904</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.655205267801205</v>
       </c>
       <c r="E93">
-        <v>-34.50917678872562</v>
+        <v>-36.15522110970058</v>
       </c>
       <c r="F93">
-        <v>5.070328209158499</v>
+        <v>5.254079979917097</v>
       </c>
       <c r="G93">
-        <v>-8.73367373233496</v>
+        <v>-10.77873393379648</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.54024867257029</v>
       </c>
       <c r="E94">
-        <v>-36.33509046236191</v>
+        <v>-38.78222487312076</v>
       </c>
       <c r="F94">
-        <v>4.401133259541725</v>
+        <v>5.000786765693481</v>
       </c>
       <c r="G94">
-        <v>-8.682389570959428</v>
+        <v>-10.53622970096174</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.365597044835503</v>
       </c>
       <c r="E95">
-        <v>-37.70848061307321</v>
+        <v>-40.9051429950182</v>
       </c>
       <c r="F95">
-        <v>4.973747196931299</v>
+        <v>4.724123650302086</v>
       </c>
       <c r="G95">
-        <v>-7.931465020334399</v>
+        <v>-10.55432738246734</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.133744197040587</v>
       </c>
       <c r="E96">
-        <v>-41.45342088164278</v>
+        <v>-42.31262270428368</v>
       </c>
       <c r="F96">
-        <v>4.694328931558193</v>
+        <v>5.087014842120492</v>
       </c>
       <c r="G96">
-        <v>-8.113670190720491</v>
+        <v>-10.31669479903961</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.851218727605617</v>
       </c>
       <c r="E97">
-        <v>-42.95308111626284</v>
+        <v>-45.77054595952551</v>
       </c>
       <c r="F97">
-        <v>4.392075890359514</v>
+        <v>5.032574536408509</v>
       </c>
       <c r="G97">
-        <v>-7.682834675316612</v>
+        <v>-10.57074766057315</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.526870640958929</v>
       </c>
       <c r="E98">
-        <v>-45.02946665847689</v>
+        <v>-47.11358132696645</v>
       </c>
       <c r="F98">
-        <v>4.446123549922572</v>
+        <v>4.958475415493288</v>
       </c>
       <c r="G98">
-        <v>-8.826019684639524</v>
+        <v>-10.59433182183697</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.179285179962395</v>
       </c>
       <c r="E99">
-        <v>-48.18845422219154</v>
+        <v>-49.00051086647863</v>
       </c>
       <c r="F99">
-        <v>4.642791225225618</v>
+        <v>4.944621799048869</v>
       </c>
       <c r="G99">
-        <v>-7.984315628464602</v>
+        <v>-10.4396752283763</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.817115011576172</v>
       </c>
       <c r="E100">
-        <v>-49.38277139851302</v>
+        <v>-51.54254615600982</v>
       </c>
       <c r="F100">
-        <v>4.128540741567686</v>
+        <v>4.749178450767159</v>
       </c>
       <c r="G100">
-        <v>-7.970250241979978</v>
+        <v>-9.903312111227329</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.475164205428136</v>
       </c>
       <c r="E101">
-        <v>-53.06085015626702</v>
+        <v>-53.37223613704322</v>
       </c>
       <c r="F101">
-        <v>3.22787674532145</v>
+        <v>5.069832845451625</v>
       </c>
       <c r="G101">
-        <v>-8.545296761735477</v>
+        <v>-9.999152545167098</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.147668165979964</v>
       </c>
       <c r="E102">
-        <v>-53.62767109315414</v>
+        <v>-55.34416426122651</v>
       </c>
       <c r="F102">
-        <v>3.278827967532842</v>
+        <v>4.840928424301232</v>
       </c>
       <c r="G102">
-        <v>-8.265272213009553</v>
+        <v>-10.29814415334746</v>
       </c>
     </row>
   </sheetData>
